--- a/PathPointsDefine.xlsx
+++ b/PathPointsDefine.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProjects\c550\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833AC1A1-0D88-4879-91B6-C6DE4AEFF0AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00C09C4-5868-42D3-A6E7-FC6844B48515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="27096" windowHeight="16296" xr2:uid="{60BF1A9E-F77C-4FB5-BF3B-E5EC594AA92E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{60BF1A9E-F77C-4FB5-BF3B-E5EC594AA92E}"/>
   </bookViews>
   <sheets>
     <sheet name="PathPoints6" sheetId="1" r:id="rId1"/>
@@ -1309,15 +1309,33 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1327,28 +1345,10 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1727,43 +1727,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479670DE-A070-4E78-B924-40F346BFE3B4}">
   <dimension ref="A1:R43"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="23.21875" style="26" customWidth="1"/>
-    <col min="2" max="2" width="12.109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="11.33203125" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
-    <col min="5" max="5" width="13.88671875" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
-    <col min="7" max="7" width="12.77734375" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="11" width="21.6640625" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" customWidth="1"/>
-    <col min="14" max="14" width="18.44140625" customWidth="1"/>
-    <col min="15" max="15" width="10.88671875" customWidth="1"/>
-    <col min="16" max="16" width="10.21875" customWidth="1"/>
-    <col min="17" max="17" width="16.77734375" customWidth="1"/>
-    <col min="18" max="18" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="23.25" style="26" customWidth="1"/>
+    <col min="2" max="2" width="12.125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="13.125" customWidth="1"/>
+    <col min="5" max="5" width="13.875" customWidth="1"/>
+    <col min="6" max="6" width="14.625" customWidth="1"/>
+    <col min="7" max="7" width="12.75" customWidth="1"/>
+    <col min="8" max="8" width="13.25" customWidth="1"/>
+    <col min="9" max="9" width="11.5" customWidth="1"/>
+    <col min="10" max="10" width="10.625" customWidth="1"/>
+    <col min="11" max="11" width="21.625" customWidth="1"/>
+    <col min="13" max="13" width="15.25" customWidth="1"/>
+    <col min="14" max="14" width="18.5" customWidth="1"/>
+    <col min="15" max="15" width="10.875" customWidth="1"/>
+    <col min="16" max="16" width="10.25" customWidth="1"/>
+    <col min="17" max="17" width="16.75" customWidth="1"/>
+    <col min="18" max="18" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A1" s="33"/>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A1" s="39"/>
       <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="31" t="s">
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="37" t="s">
         <v>123</v>
       </c>
       <c r="L1" s="2"/>
@@ -1774,22 +1774,22 @@
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A2" s="39"/>
       <c r="B2" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="32"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="38"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1798,21 +1798,21 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="33"/>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A3" s="39"/>
       <c r="B3" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
       <c r="K3" s="12" t="s">
         <v>119</v>
       </c>
@@ -1826,8 +1826,8 @@
       </c>
       <c r="R3" s="2"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="33"/>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
+      <c r="A4" s="39"/>
       <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A5" s="22" t="s">
         <v>71</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="3" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" s="3" customFormat="1" ht="95.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="23" t="s">
         <v>30</v>
       </c>
@@ -1974,14 +1974,14 @@
         <v>80</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="24" t="s">
         <v>31</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="28" t="s">
         <v>82</v>
       </c>
       <c r="D7" s="2"/>
@@ -2002,14 +2002,14 @@
       <c r="Q7" s="2"/>
       <c r="R7" s="2"/>
     </row>
-    <row r="8" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="24" t="s">
         <v>32</v>
       </c>
       <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="9" t="s">
@@ -2030,14 +2030,14 @@
       <c r="Q8" s="2"/>
       <c r="R8" s="2"/>
     </row>
-    <row r="9" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="24" t="s">
         <v>33</v>
       </c>
       <c r="B9" s="6">
         <v>3</v>
       </c>
-      <c r="C9" s="30"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="10" t="s">
         <v>65</v>
       </c>
@@ -2060,14 +2060,14 @@
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
     </row>
-    <row r="10" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="24" t="s">
         <v>34</v>
       </c>
       <c r="B10" s="6">
         <v>4</v>
       </c>
-      <c r="C10" s="30"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="9" t="s">
@@ -2088,14 +2088,14 @@
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
     </row>
-    <row r="11" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="24" t="s">
         <v>35</v>
       </c>
       <c r="B11" s="6">
         <v>5</v>
       </c>
-      <c r="C11" s="30"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="9" t="s">
@@ -2116,14 +2116,14 @@
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
     </row>
-    <row r="12" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="24" t="s">
         <v>36</v>
       </c>
       <c r="B12" s="6">
         <v>6</v>
       </c>
-      <c r="C12" s="30"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="9" t="s">
@@ -2144,14 +2144,14 @@
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
     </row>
-    <row r="13" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
+    <row r="13" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A13" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="28">
         <v>8</v>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="16" t="s">
         <v>65</v>
       </c>
@@ -2182,19 +2182,19 @@
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
     </row>
-    <row r="14" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="35"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="36" t="s">
+    <row r="14" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A14" s="40"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2204,14 +2204,14 @@
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
     </row>
-    <row r="15" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+    <row r="15" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A15" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="28">
         <v>9</v>
       </c>
-      <c r="C15" s="30"/>
+      <c r="C15" s="28"/>
       <c r="D15" s="16" t="s">
         <v>65</v>
       </c>
@@ -2242,17 +2242,17 @@
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
     </row>
-    <row r="16" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="35"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
+    <row r="16" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A16" s="40"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -2262,19 +2262,19 @@
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
     </row>
-    <row r="17" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="35"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="36" t="s">
+    <row r="17" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A17" s="40"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2284,14 +2284,14 @@
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
     </row>
-    <row r="18" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="24" t="s">
         <v>49</v>
       </c>
       <c r="B18" s="6">
         <v>14</v>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="28"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9" t="s">
@@ -2314,14 +2314,14 @@
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
     </row>
-    <row r="19" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="28" t="s">
+    <row r="19" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A19" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="29">
         <v>15</v>
       </c>
-      <c r="C19" s="30"/>
+      <c r="C19" s="28"/>
       <c r="D19" s="16" t="s">
         <v>65</v>
       </c>
@@ -2348,19 +2348,19 @@
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
     </row>
-    <row r="20" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="36" t="s">
+    <row r="20" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A20" s="36"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2370,14 +2370,14 @@
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
     </row>
-    <row r="21" spans="1:18" s="3" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" s="3" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="25" t="s">
         <v>51</v>
       </c>
       <c r="B21" s="15">
         <v>16</v>
       </c>
-      <c r="C21" s="30"/>
+      <c r="C21" s="28"/>
       <c r="D21" s="14"/>
       <c r="E21" s="10" t="s">
         <v>65</v>
@@ -2406,14 +2406,14 @@
       <c r="Q21" s="14"/>
       <c r="R21" s="14"/>
     </row>
-    <row r="22" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="24" t="s">
         <v>52</v>
       </c>
       <c r="B22" s="6">
         <v>11</v>
       </c>
-      <c r="C22" s="30"/>
+      <c r="C22" s="28"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="11" t="s">
@@ -2434,14 +2434,14 @@
       </c>
       <c r="R22" s="2"/>
     </row>
-    <row r="23" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="24" t="s">
         <v>37</v>
       </c>
       <c r="B23" s="6">
         <v>21</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="29" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="2"/>
@@ -2460,23 +2460,23 @@
       <c r="Q23" s="2"/>
       <c r="R23" s="2"/>
     </row>
-    <row r="24" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="24" t="s">
         <v>38</v>
       </c>
       <c r="B24" s="6">
         <v>91</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="30" t="s">
+      <c r="C24" s="32"/>
+      <c r="D24" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -2486,23 +2486,23 @@
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
     </row>
-    <row r="25" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="24" t="s">
         <v>39</v>
       </c>
       <c r="B25" s="6">
         <v>92</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="30" t="s">
+      <c r="C25" s="32"/>
+      <c r="D25" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2512,23 +2512,23 @@
       <c r="Q25" s="2"/>
       <c r="R25" s="2"/>
     </row>
-    <row r="26" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="24" t="s">
         <v>42</v>
       </c>
       <c r="B26" s="6">
         <v>93</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="30" t="s">
+      <c r="C26" s="32"/>
+      <c r="D26" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2538,23 +2538,23 @@
       <c r="Q26" s="2"/>
       <c r="R26" s="2"/>
     </row>
-    <row r="27" spans="1:18" s="3" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" s="3" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="25" t="s">
         <v>43</v>
       </c>
       <c r="B27" s="15">
         <v>31</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="41" t="s">
+      <c r="C27" s="32"/>
+      <c r="D27" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
@@ -2564,21 +2564,21 @@
       <c r="Q27" s="14"/>
       <c r="R27" s="14"/>
     </row>
-    <row r="28" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="24" t="s">
         <v>44</v>
       </c>
       <c r="B28" s="6">
         <v>32</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -2588,14 +2588,14 @@
       <c r="Q28" s="2"/>
       <c r="R28" s="2"/>
     </row>
-    <row r="29" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="24" t="s">
         <v>45</v>
       </c>
       <c r="B29" s="6">
         <v>33</v>
       </c>
-      <c r="C29" s="39"/>
+      <c r="C29" s="32"/>
       <c r="D29" s="9" t="s">
         <v>96</v>
       </c>
@@ -2620,14 +2620,14 @@
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
     </row>
-    <row r="30" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="24" t="s">
         <v>46</v>
       </c>
       <c r="B30" s="6">
         <v>35</v>
       </c>
-      <c r="C30" s="39"/>
+      <c r="C30" s="32"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -2644,14 +2644,14 @@
       <c r="Q30" s="2"/>
       <c r="R30" s="2"/>
     </row>
-    <row r="31" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="24" t="s">
         <v>47</v>
       </c>
       <c r="B31" s="6">
         <v>36</v>
       </c>
-      <c r="C31" s="39"/>
+      <c r="C31" s="32"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -2668,14 +2668,14 @@
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
     </row>
-    <row r="32" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="28" t="s">
+    <row r="32" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="37">
+      <c r="B32" s="29">
         <v>37</v>
       </c>
-      <c r="C32" s="39"/>
+      <c r="C32" s="32"/>
       <c r="D32" s="9" t="s">
         <v>96</v>
       </c>
@@ -2702,10 +2702,10 @@
       <c r="Q32" s="2"/>
       <c r="R32" s="2"/>
     </row>
-    <row r="33" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="29"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
+    <row r="33" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="36"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="32"/>
       <c r="D33" s="21"/>
       <c r="E33" s="11" t="s">
         <v>116</v>
@@ -2730,21 +2730,20 @@
       <c r="Q33" s="2"/>
       <c r="R33" s="2"/>
     </row>
-    <row r="34" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="24" t="s">
         <v>53</v>
       </c>
       <c r="B34" s="6">
         <v>22</v>
       </c>
-      <c r="C34" s="39"/>
+      <c r="C34" s="32"/>
       <c r="D34" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="E34" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
       <c r="I34" s="2"/>
@@ -2758,21 +2757,20 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
     </row>
-    <row r="35" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="24" t="s">
         <v>54</v>
       </c>
       <c r="B35" s="6">
         <v>23</v>
       </c>
-      <c r="C35" s="39"/>
+      <c r="C35" s="32"/>
       <c r="D35" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E35" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="E35" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="I35" s="2"/>
@@ -2786,14 +2784,14 @@
       <c r="Q35" s="2"/>
       <c r="R35" s="2"/>
     </row>
-    <row r="36" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="24" t="s">
         <v>55</v>
       </c>
       <c r="B36" s="6">
         <v>24</v>
       </c>
-      <c r="C36" s="39"/>
+      <c r="C36" s="32"/>
       <c r="D36" s="11" t="s">
         <v>102</v>
       </c>
@@ -2814,14 +2812,14 @@
       <c r="Q36" s="2"/>
       <c r="R36" s="2"/>
     </row>
-    <row r="37" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="24" t="s">
         <v>56</v>
       </c>
       <c r="B37" s="6">
         <v>25</v>
       </c>
-      <c r="C37" s="39"/>
+      <c r="C37" s="32"/>
       <c r="D37" s="11" t="s">
         <v>102</v>
       </c>
@@ -2842,14 +2840,14 @@
       <c r="Q37" s="2"/>
       <c r="R37" s="2"/>
     </row>
-    <row r="38" spans="1:18" ht="68.400000000000006" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="68.45" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="24" t="s">
         <v>57</v>
       </c>
       <c r="B38" s="6">
         <v>26</v>
       </c>
-      <c r="C38" s="39"/>
+      <c r="C38" s="32"/>
       <c r="D38" s="11" t="s">
         <v>104</v>
       </c>
@@ -2878,14 +2876,14 @@
       <c r="Q38" s="2"/>
       <c r="R38" s="2"/>
     </row>
-    <row r="39" spans="1:18" ht="70.2" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="70.150000000000006" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="24" t="s">
         <v>58</v>
       </c>
       <c r="B39" s="6">
         <v>27</v>
       </c>
-      <c r="C39" s="39"/>
+      <c r="C39" s="32"/>
       <c r="D39" s="11" t="s">
         <v>104</v>
       </c>
@@ -2912,14 +2910,14 @@
       <c r="Q39" s="2"/>
       <c r="R39" s="2"/>
     </row>
-    <row r="40" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="24" t="s">
         <v>128</v>
       </c>
       <c r="B40" s="6">
         <v>28</v>
       </c>
-      <c r="C40" s="39"/>
+      <c r="C40" s="32"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
@@ -2936,14 +2934,14 @@
       <c r="Q40" s="2"/>
       <c r="R40" s="2"/>
     </row>
-    <row r="41" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="24" t="s">
         <v>59</v>
       </c>
       <c r="B41" s="6">
         <v>38</v>
       </c>
-      <c r="C41" s="39"/>
+      <c r="C41" s="32"/>
       <c r="D41" s="11" t="s">
         <v>110</v>
       </c>
@@ -2962,14 +2960,14 @@
       <c r="Q41" s="2"/>
       <c r="R41" s="2"/>
     </row>
-    <row r="42" spans="1:18" s="3" customFormat="1" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" s="3" customFormat="1" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="25" t="s">
         <v>129</v>
       </c>
       <c r="B42" s="15">
         <v>41</v>
       </c>
-      <c r="C42" s="39"/>
+      <c r="C42" s="32"/>
       <c r="D42" s="11" t="s">
         <v>133</v>
       </c>
@@ -2992,14 +2990,14 @@
       <c r="Q42" s="14"/>
       <c r="R42" s="14"/>
     </row>
-    <row r="43" spans="1:18" ht="43.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="24" t="s">
         <v>130</v>
       </c>
       <c r="B43" s="6">
         <v>42</v>
       </c>
-      <c r="C43" s="39"/>
+      <c r="C43" s="32"/>
       <c r="D43" s="11" t="s">
         <v>131</v>
       </c>
@@ -3026,14 +3024,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="C23:C43"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="D27:J27"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="D25:J25"/>
     <mergeCell ref="K1:K2"/>
@@ -3050,6 +3040,14 @@
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="D20:J20"/>
     <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="C23:C43"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="D27:J27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3059,13 +3057,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CDFC60C-710B-4C1F-AF4A-9B195BAE2766}">
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="7" max="7" width="22.6640625" style="4" customWidth="1"/>
+    <col min="7" max="7" width="22.625" style="4" customWidth="1"/>
     <col min="8" max="8" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1">
         <v>13</v>
       </c>
@@ -3074,7 +3072,7 @@
         <v>14.0625</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="G13" s="27" t="s">
         <v>126</v>
       </c>
@@ -3082,7 +3080,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.15">
       <c r="G14" s="6" t="s">
         <v>31</v>
       </c>
@@ -3090,7 +3088,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.15">
       <c r="G15" s="6" t="s">
         <v>32</v>
       </c>
@@ -3098,7 +3096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.15">
       <c r="G16" s="6" t="s">
         <v>33</v>
       </c>
@@ -3106,7 +3104,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G17" s="6" t="s">
         <v>34</v>
       </c>
@@ -3114,7 +3112,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G18" s="6" t="s">
         <v>35</v>
       </c>
@@ -3122,7 +3120,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G19" s="6" t="s">
         <v>36</v>
       </c>
@@ -3130,7 +3128,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G20" s="6" t="s">
         <v>40</v>
       </c>
@@ -3138,7 +3136,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G21" s="6" t="s">
         <v>41</v>
       </c>
@@ -3146,7 +3144,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G22" s="6" t="s">
         <v>49</v>
       </c>
@@ -3154,7 +3152,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G23" s="6" t="s">
         <v>50</v>
       </c>
@@ -3162,7 +3160,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G24" s="15" t="s">
         <v>51</v>
       </c>
@@ -3170,7 +3168,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G25" s="6" t="s">
         <v>52</v>
       </c>
@@ -3178,7 +3176,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G26" s="6" t="s">
         <v>37</v>
       </c>
@@ -3186,7 +3184,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G27" s="6" t="s">
         <v>38</v>
       </c>
@@ -3194,7 +3192,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="28" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G28" s="6" t="s">
         <v>39</v>
       </c>
@@ -3202,7 +3200,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="29" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G29" s="6" t="s">
         <v>42</v>
       </c>
@@ -3210,7 +3208,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="30" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G30" s="15" t="s">
         <v>43</v>
       </c>
@@ -3218,7 +3216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G31" s="6" t="s">
         <v>44</v>
       </c>
@@ -3226,7 +3224,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="32" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G32" s="6" t="s">
         <v>45</v>
       </c>
@@ -3234,7 +3232,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="33" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G33" s="6" t="s">
         <v>46</v>
       </c>
@@ -3242,7 +3240,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G34" s="6" t="s">
         <v>47</v>
       </c>
@@ -3250,7 +3248,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G35" s="6" t="s">
         <v>48</v>
       </c>
@@ -3258,7 +3256,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G36" s="6" t="s">
         <v>53</v>
       </c>
@@ -3266,7 +3264,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G37" s="6" t="s">
         <v>54</v>
       </c>
@@ -3274,7 +3272,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G38" s="6" t="s">
         <v>55</v>
       </c>
@@ -3282,7 +3280,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G39" s="6" t="s">
         <v>56</v>
       </c>
@@ -3290,7 +3288,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="40" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G40" s="6" t="s">
         <v>57</v>
       </c>
@@ -3298,7 +3296,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="41" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G41" s="6" t="s">
         <v>58</v>
       </c>
@@ -3306,7 +3304,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="42" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G42" s="6" t="s">
         <v>59</v>
       </c>
@@ -3314,7 +3312,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="43" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G43" s="15" t="s">
         <v>129</v>
       </c>
@@ -3322,7 +3320,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="7:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="7:8" x14ac:dyDescent="0.15">
       <c r="G44" s="6" t="s">
         <v>130</v>
       </c>

--- a/PathPointsDefine.xlsx
+++ b/PathPointsDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProjects\c550\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00C09C4-5868-42D3-A6E7-FC6844B48515}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5CAA47-5524-4157-8E95-977630CBA8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{60BF1A9E-F77C-4FB5-BF3B-E5EC594AA92E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="139">
   <si>
     <t>命令形式</t>
   </si>
@@ -544,6 +544,10 @@
   <si>
     <t>全局变量位置</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>1-扶持打开、
+-1-扶持锁紧</t>
   </si>
 </sst>
 </file>
@@ -1309,18 +1313,39 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1328,27 +1353,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1749,21 +1753,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A1" s="39"/>
+      <c r="A1" s="33"/>
       <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="37" t="s">
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="31" t="s">
         <v>123</v>
       </c>
       <c r="L1" s="2"/>
@@ -1775,21 +1779,21 @@
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A2" s="39"/>
+      <c r="A2" s="33"/>
       <c r="B2" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="31" t="s">
+      <c r="D2" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="J2" s="31"/>
-      <c r="K2" s="38"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="32"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1799,20 +1803,20 @@
       <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A3" s="39"/>
+      <c r="A3" s="33"/>
       <c r="B3" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="31" t="s">
+      <c r="D3" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="31"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="31"/>
-      <c r="I3" s="31"/>
-      <c r="J3" s="31"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="I3" s="34"/>
+      <c r="J3" s="34"/>
       <c r="K3" s="12" t="s">
         <v>119</v>
       </c>
@@ -1827,7 +1831,7 @@
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A4" s="39"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
@@ -1981,7 +1985,7 @@
       <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="30" t="s">
         <v>82</v>
       </c>
       <c r="D7" s="2"/>
@@ -2009,7 +2013,7 @@
       <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" s="28"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="9" t="s">
@@ -2037,7 +2041,7 @@
       <c r="B9" s="6">
         <v>3</v>
       </c>
-      <c r="C9" s="28"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="10" t="s">
         <v>65</v>
       </c>
@@ -2067,7 +2071,7 @@
       <c r="B10" s="6">
         <v>4</v>
       </c>
-      <c r="C10" s="28"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="9" t="s">
@@ -2095,7 +2099,7 @@
       <c r="B11" s="6">
         <v>5</v>
       </c>
-      <c r="C11" s="28"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="9" t="s">
@@ -2123,7 +2127,7 @@
       <c r="B12" s="6">
         <v>6</v>
       </c>
-      <c r="C12" s="28"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="9" t="s">
@@ -2145,13 +2149,13 @@
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="40" t="s">
+      <c r="A13" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="28">
+      <c r="B13" s="30">
         <v>8</v>
       </c>
-      <c r="C13" s="28"/>
+      <c r="C13" s="30"/>
       <c r="D13" s="16" t="s">
         <v>65</v>
       </c>
@@ -2183,18 +2187,18 @@
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="40"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="41" t="s">
+      <c r="A14" s="35"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
+      <c r="H14" s="36"/>
+      <c r="I14" s="36"/>
+      <c r="J14" s="36"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2205,13 +2209,13 @@
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="35" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="28">
+      <c r="B15" s="30">
         <v>9</v>
       </c>
-      <c r="C15" s="28"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="16" t="s">
         <v>65</v>
       </c>
@@ -2243,16 +2247,16 @@
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="40"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
+      <c r="A16" s="35"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40"/>
+      <c r="J16" s="40"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -2263,18 +2267,18 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="40"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="41" t="s">
+      <c r="A17" s="35"/>
+      <c r="B17" s="30"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="36"/>
+      <c r="G17" s="36"/>
+      <c r="H17" s="36"/>
+      <c r="I17" s="36"/>
+      <c r="J17" s="36"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2291,7 +2295,7 @@
       <c r="B18" s="6">
         <v>14</v>
       </c>
-      <c r="C18" s="28"/>
+      <c r="C18" s="30"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9" t="s">
@@ -2315,13 +2319,13 @@
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="35" t="s">
+      <c r="A19" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="37">
         <v>15</v>
       </c>
-      <c r="C19" s="28"/>
+      <c r="C19" s="30"/>
       <c r="D19" s="16" t="s">
         <v>65</v>
       </c>
@@ -2349,18 +2353,18 @@
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="36"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="41" t="s">
+      <c r="A20" s="29"/>
+      <c r="B20" s="38"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
+      <c r="E20" s="36"/>
+      <c r="F20" s="36"/>
+      <c r="G20" s="36"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="36"/>
+      <c r="J20" s="36"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2377,7 +2381,7 @@
       <c r="B21" s="15">
         <v>16</v>
       </c>
-      <c r="C21" s="28"/>
+      <c r="C21" s="30"/>
       <c r="D21" s="14"/>
       <c r="E21" s="10" t="s">
         <v>65</v>
@@ -2413,7 +2417,7 @@
       <c r="B22" s="6">
         <v>11</v>
       </c>
-      <c r="C22" s="28"/>
+      <c r="C22" s="30"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="11" t="s">
@@ -2441,7 +2445,7 @@
       <c r="B23" s="6">
         <v>21</v>
       </c>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="37" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="2"/>
@@ -2467,16 +2471,16 @@
       <c r="B24" s="6">
         <v>91</v>
       </c>
-      <c r="C24" s="32"/>
-      <c r="D24" s="28" t="s">
+      <c r="C24" s="39"/>
+      <c r="D24" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
+      <c r="E24" s="30"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="30"/>
+      <c r="I24" s="30"/>
+      <c r="J24" s="30"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -2493,16 +2497,16 @@
       <c r="B25" s="6">
         <v>92</v>
       </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="28" t="s">
+      <c r="C25" s="39"/>
+      <c r="D25" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="30"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2519,16 +2523,16 @@
       <c r="B26" s="6">
         <v>93</v>
       </c>
-      <c r="C26" s="32"/>
-      <c r="D26" s="28" t="s">
+      <c r="C26" s="39"/>
+      <c r="D26" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2545,16 +2549,16 @@
       <c r="B27" s="15">
         <v>31</v>
       </c>
-      <c r="C27" s="32"/>
-      <c r="D27" s="34" t="s">
+      <c r="C27" s="39"/>
+      <c r="D27" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="34"/>
-      <c r="J27" s="34"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
@@ -2571,14 +2575,14 @@
       <c r="B28" s="6">
         <v>32</v>
       </c>
-      <c r="C28" s="32"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
+      <c r="I28" s="30"/>
+      <c r="J28" s="30"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -2595,7 +2599,7 @@
       <c r="B29" s="6">
         <v>33</v>
       </c>
-      <c r="C29" s="32"/>
+      <c r="C29" s="39"/>
       <c r="D29" s="9" t="s">
         <v>96</v>
       </c>
@@ -2627,7 +2631,7 @@
       <c r="B30" s="6">
         <v>35</v>
       </c>
-      <c r="C30" s="32"/>
+      <c r="C30" s="39"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -2651,7 +2655,7 @@
       <c r="B31" s="6">
         <v>36</v>
       </c>
-      <c r="C31" s="32"/>
+      <c r="C31" s="39"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -2669,13 +2673,13 @@
       <c r="R31" s="2"/>
     </row>
     <row r="32" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="35" t="s">
+      <c r="A32" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="29">
+      <c r="B32" s="37">
         <v>37</v>
       </c>
-      <c r="C32" s="32"/>
+      <c r="C32" s="39"/>
       <c r="D32" s="9" t="s">
         <v>96</v>
       </c>
@@ -2703,9 +2707,9 @@
       <c r="R32" s="2"/>
     </row>
     <row r="33" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="36"/>
-      <c r="B33" s="30"/>
-      <c r="C33" s="32"/>
+      <c r="A33" s="29"/>
+      <c r="B33" s="38"/>
+      <c r="C33" s="39"/>
       <c r="D33" s="21"/>
       <c r="E33" s="11" t="s">
         <v>116</v>
@@ -2737,7 +2741,7 @@
       <c r="B34" s="6">
         <v>22</v>
       </c>
-      <c r="C34" s="32"/>
+      <c r="C34" s="39"/>
       <c r="D34" s="11" t="s">
         <v>99</v>
       </c>
@@ -2764,7 +2768,7 @@
       <c r="B35" s="6">
         <v>23</v>
       </c>
-      <c r="C35" s="32"/>
+      <c r="C35" s="39"/>
       <c r="D35" s="11" t="s">
         <v>99</v>
       </c>
@@ -2791,14 +2795,16 @@
       <c r="B36" s="6">
         <v>24</v>
       </c>
-      <c r="C36" s="32"/>
+      <c r="C36" s="39"/>
       <c r="D36" s="11" t="s">
         <v>102</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F36" s="2"/>
+      <c r="F36" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="G36" s="2"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
@@ -2819,14 +2825,16 @@
       <c r="B37" s="6">
         <v>25</v>
       </c>
-      <c r="C37" s="32"/>
+      <c r="C37" s="39"/>
       <c r="D37" s="11" t="s">
         <v>102</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F37" s="2"/>
+      <c r="F37" s="11" t="s">
+        <v>138</v>
+      </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
       <c r="I37" s="2"/>
@@ -2847,7 +2855,7 @@
       <c r="B38" s="6">
         <v>26</v>
       </c>
-      <c r="C38" s="32"/>
+      <c r="C38" s="39"/>
       <c r="D38" s="11" t="s">
         <v>104</v>
       </c>
@@ -2883,7 +2891,7 @@
       <c r="B39" s="6">
         <v>27</v>
       </c>
-      <c r="C39" s="32"/>
+      <c r="C39" s="39"/>
       <c r="D39" s="11" t="s">
         <v>104</v>
       </c>
@@ -2917,7 +2925,7 @@
       <c r="B40" s="6">
         <v>28</v>
       </c>
-      <c r="C40" s="32"/>
+      <c r="C40" s="39"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
@@ -2941,7 +2949,7 @@
       <c r="B41" s="6">
         <v>38</v>
       </c>
-      <c r="C41" s="32"/>
+      <c r="C41" s="39"/>
       <c r="D41" s="11" t="s">
         <v>110</v>
       </c>
@@ -2967,7 +2975,7 @@
       <c r="B42" s="15">
         <v>41</v>
       </c>
-      <c r="C42" s="32"/>
+      <c r="C42" s="39"/>
       <c r="D42" s="11" t="s">
         <v>133</v>
       </c>
@@ -2997,7 +3005,7 @@
       <c r="B43" s="6">
         <v>42</v>
       </c>
-      <c r="C43" s="32"/>
+      <c r="C43" s="39"/>
       <c r="D43" s="11" t="s">
         <v>131</v>
       </c>
@@ -3024,6 +3032,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="C23:C43"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="D27:J27"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="D25:J25"/>
     <mergeCell ref="K1:K2"/>
@@ -3040,14 +3056,6 @@
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="D20:J20"/>
     <mergeCell ref="B32:B33"/>
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="C23:C43"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="D27:J27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/PathPointsDefine.xlsx
+++ b/PathPointsDefine.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyProjects\c550\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF5CAA47-5524-4157-8E95-977630CBA8F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E84802BF-2E49-47CF-8849-DB3CFFD7C4A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{60BF1A9E-F77C-4FB5-BF3B-E5EC594AA92E}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="144">
   <si>
     <t>命令形式</t>
   </si>
@@ -548,6 +548,21 @@
   <si>
     <t>1-扶持打开、
 -1-扶持锁紧</t>
+  </si>
+  <si>
+    <t>本地-极坐标运行</t>
+  </si>
+  <si>
+    <t>本地-极坐标判断</t>
+  </si>
+  <si>
+    <t>p1 导轨</t>
+  </si>
+  <si>
+    <t>p2 旋转</t>
+  </si>
+  <si>
+    <t>p3 伸缩</t>
   </si>
 </sst>
 </file>
@@ -1313,15 +1328,33 @@
     <xf numFmtId="0" fontId="0" fillId="36" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1331,28 +1364,10 @@
     <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1730,7 +1745,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{479670DE-A070-4E78-B924-40F346BFE3B4}">
-  <dimension ref="A1:R43"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23.25" style="26" customWidth="1"/>
@@ -1753,21 +1768,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A1" s="33"/>
+      <c r="A1" s="39"/>
       <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
       <c r="C1" s="1"/>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="31" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="31" t="s">
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="37" t="s">
         <v>123</v>
       </c>
       <c r="L1" s="2"/>
@@ -1779,21 +1794,21 @@
       <c r="R1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A2" s="33"/>
+      <c r="A2" s="39"/>
       <c r="B2" s="5" t="s">
         <v>117</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="31" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="32"/>
+      <c r="E2" s="31"/>
+      <c r="F2" s="31"/>
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="38"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1803,20 +1818,20 @@
       <c r="R2" s="2"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A3" s="33"/>
+      <c r="A3" s="39"/>
       <c r="B3" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="34" t="s">
+      <c r="D3" s="31" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="34"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="31"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
       <c r="K3" s="12" t="s">
         <v>119</v>
       </c>
@@ -1831,7 +1846,7 @@
       <c r="R3" s="2"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.15">
-      <c r="A4" s="33"/>
+      <c r="A4" s="39"/>
       <c r="B4" s="5" t="s">
         <v>0</v>
       </c>
@@ -1985,7 +2000,7 @@
       <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="28" t="s">
         <v>82</v>
       </c>
       <c r="D7" s="2"/>
@@ -2013,7 +2028,7 @@
       <c r="B8" s="6">
         <v>2</v>
       </c>
-      <c r="C8" s="30"/>
+      <c r="C8" s="28"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="F8" s="9" t="s">
@@ -2041,7 +2056,7 @@
       <c r="B9" s="6">
         <v>3</v>
       </c>
-      <c r="C9" s="30"/>
+      <c r="C9" s="28"/>
       <c r="D9" s="10" t="s">
         <v>65</v>
       </c>
@@ -2071,7 +2086,7 @@
       <c r="B10" s="6">
         <v>4</v>
       </c>
-      <c r="C10" s="30"/>
+      <c r="C10" s="28"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="9" t="s">
@@ -2099,7 +2114,7 @@
       <c r="B11" s="6">
         <v>5</v>
       </c>
-      <c r="C11" s="30"/>
+      <c r="C11" s="28"/>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="9" t="s">
@@ -2127,7 +2142,7 @@
       <c r="B12" s="6">
         <v>6</v>
       </c>
-      <c r="C12" s="30"/>
+      <c r="C12" s="28"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
       <c r="F12" s="9" t="s">
@@ -2149,13 +2164,13 @@
       <c r="R12" s="2"/>
     </row>
     <row r="13" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="35" t="s">
+      <c r="A13" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="28">
         <v>8</v>
       </c>
-      <c r="C13" s="30"/>
+      <c r="C13" s="28"/>
       <c r="D13" s="16" t="s">
         <v>65</v>
       </c>
@@ -2187,18 +2202,18 @@
       <c r="R13" s="2"/>
     </row>
     <row r="14" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="35"/>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="36" t="s">
+      <c r="A14" s="40"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="41" t="s">
         <v>85</v>
       </c>
-      <c r="E14" s="36"/>
-      <c r="F14" s="36"/>
-      <c r="G14" s="36"/>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -2209,13 +2224,13 @@
       <c r="R14" s="2"/>
     </row>
     <row r="15" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="35" t="s">
+      <c r="A15" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="28">
         <v>9</v>
       </c>
-      <c r="C15" s="30"/>
+      <c r="C15" s="28"/>
       <c r="D15" s="16" t="s">
         <v>65</v>
       </c>
@@ -2247,16 +2262,16 @@
       <c r="R15" s="2"/>
     </row>
     <row r="16" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="35"/>
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="40"/>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="40"/>
+      <c r="A16" s="40"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -2267,18 +2282,18 @@
       <c r="R16" s="2"/>
     </row>
     <row r="17" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="35"/>
-      <c r="B17" s="30"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="36" t="s">
+      <c r="A17" s="40"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -2295,7 +2310,7 @@
       <c r="B18" s="6">
         <v>14</v>
       </c>
-      <c r="C18" s="30"/>
+      <c r="C18" s="28"/>
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
       <c r="F18" s="9" t="s">
@@ -2319,13 +2334,13 @@
       <c r="R18" s="2"/>
     </row>
     <row r="19" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="29">
         <v>15</v>
       </c>
-      <c r="C19" s="30"/>
+      <c r="C19" s="28"/>
       <c r="D19" s="16" t="s">
         <v>65</v>
       </c>
@@ -2353,18 +2368,18 @@
       <c r="R19" s="2"/>
     </row>
     <row r="20" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="29"/>
-      <c r="B20" s="38"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="36" t="s">
+      <c r="A20" s="36"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="36"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -2381,7 +2396,7 @@
       <c r="B21" s="15">
         <v>16</v>
       </c>
-      <c r="C21" s="30"/>
+      <c r="C21" s="28"/>
       <c r="D21" s="14"/>
       <c r="E21" s="10" t="s">
         <v>65</v>
@@ -2417,7 +2432,7 @@
       <c r="B22" s="6">
         <v>11</v>
       </c>
-      <c r="C22" s="30"/>
+      <c r="C22" s="28"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="11" t="s">
@@ -2445,7 +2460,7 @@
       <c r="B23" s="6">
         <v>21</v>
       </c>
-      <c r="C23" s="37" t="s">
+      <c r="C23" s="29" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="2"/>
@@ -2471,16 +2486,16 @@
       <c r="B24" s="6">
         <v>91</v>
       </c>
-      <c r="C24" s="39"/>
-      <c r="D24" s="30" t="s">
+      <c r="C24" s="32"/>
+      <c r="D24" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="30"/>
-      <c r="H24" s="30"/>
-      <c r="I24" s="30"/>
-      <c r="J24" s="30"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -2497,16 +2512,16 @@
       <c r="B25" s="6">
         <v>92</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="30" t="s">
+      <c r="C25" s="32"/>
+      <c r="D25" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="30"/>
-      <c r="J25" s="30"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -2523,16 +2538,16 @@
       <c r="B26" s="6">
         <v>93</v>
       </c>
-      <c r="C26" s="39"/>
-      <c r="D26" s="30" t="s">
+      <c r="C26" s="32"/>
+      <c r="D26" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
+      <c r="E26" s="28"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -2549,16 +2564,16 @@
       <c r="B27" s="15">
         <v>31</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="41" t="s">
+      <c r="C27" s="32"/>
+      <c r="D27" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="41"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41"/>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+      <c r="G27" s="34"/>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
       <c r="K27" s="14"/>
       <c r="L27" s="14"/>
       <c r="M27" s="14"/>
@@ -2575,14 +2590,14 @@
       <c r="B28" s="6">
         <v>32</v>
       </c>
-      <c r="C28" s="39"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="30"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -2599,7 +2614,7 @@
       <c r="B29" s="6">
         <v>33</v>
       </c>
-      <c r="C29" s="39"/>
+      <c r="C29" s="32"/>
       <c r="D29" s="9" t="s">
         <v>96</v>
       </c>
@@ -2631,7 +2646,7 @@
       <c r="B30" s="6">
         <v>35</v>
       </c>
-      <c r="C30" s="39"/>
+      <c r="C30" s="32"/>
       <c r="D30" s="2"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
@@ -2655,7 +2670,7 @@
       <c r="B31" s="6">
         <v>36</v>
       </c>
-      <c r="C31" s="39"/>
+      <c r="C31" s="32"/>
       <c r="D31" s="2"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
@@ -2673,13 +2688,13 @@
       <c r="R31" s="2"/>
     </row>
     <row r="32" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="B32" s="37">
+      <c r="B32" s="29">
         <v>37</v>
       </c>
-      <c r="C32" s="39"/>
+      <c r="C32" s="32"/>
       <c r="D32" s="9" t="s">
         <v>96</v>
       </c>
@@ -2707,9 +2722,9 @@
       <c r="R32" s="2"/>
     </row>
     <row r="33" spans="1:18" ht="43.9" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="29"/>
-      <c r="B33" s="38"/>
-      <c r="C33" s="39"/>
+      <c r="A33" s="36"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="32"/>
       <c r="D33" s="21"/>
       <c r="E33" s="11" t="s">
         <v>116</v>
@@ -2741,7 +2756,7 @@
       <c r="B34" s="6">
         <v>22</v>
       </c>
-      <c r="C34" s="39"/>
+      <c r="C34" s="32"/>
       <c r="D34" s="11" t="s">
         <v>99</v>
       </c>
@@ -2768,7 +2783,7 @@
       <c r="B35" s="6">
         <v>23</v>
       </c>
-      <c r="C35" s="39"/>
+      <c r="C35" s="32"/>
       <c r="D35" s="11" t="s">
         <v>99</v>
       </c>
@@ -2795,7 +2810,7 @@
       <c r="B36" s="6">
         <v>24</v>
       </c>
-      <c r="C36" s="39"/>
+      <c r="C36" s="32"/>
       <c r="D36" s="11" t="s">
         <v>102</v>
       </c>
@@ -2825,7 +2840,7 @@
       <c r="B37" s="6">
         <v>25</v>
       </c>
-      <c r="C37" s="39"/>
+      <c r="C37" s="32"/>
       <c r="D37" s="11" t="s">
         <v>102</v>
       </c>
@@ -2855,7 +2870,7 @@
       <c r="B38" s="6">
         <v>26</v>
       </c>
-      <c r="C38" s="39"/>
+      <c r="C38" s="32"/>
       <c r="D38" s="11" t="s">
         <v>104</v>
       </c>
@@ -2891,7 +2906,7 @@
       <c r="B39" s="6">
         <v>27</v>
       </c>
-      <c r="C39" s="39"/>
+      <c r="C39" s="32"/>
       <c r="D39" s="11" t="s">
         <v>104</v>
       </c>
@@ -2925,7 +2940,7 @@
       <c r="B40" s="6">
         <v>28</v>
       </c>
-      <c r="C40" s="39"/>
+      <c r="C40" s="32"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
@@ -2949,7 +2964,7 @@
       <c r="B41" s="6">
         <v>38</v>
       </c>
-      <c r="C41" s="39"/>
+      <c r="C41" s="32"/>
       <c r="D41" s="11" t="s">
         <v>110</v>
       </c>
@@ -2975,7 +2990,7 @@
       <c r="B42" s="15">
         <v>41</v>
       </c>
-      <c r="C42" s="39"/>
+      <c r="C42" s="32"/>
       <c r="D42" s="11" t="s">
         <v>133</v>
       </c>
@@ -3005,7 +3020,7 @@
       <c r="B43" s="6">
         <v>42</v>
       </c>
-      <c r="C43" s="39"/>
+      <c r="C43" s="32"/>
       <c r="D43" s="11" t="s">
         <v>131</v>
       </c>
@@ -3030,16 +3045,43 @@
       <c r="Q43" s="2"/>
       <c r="R43" s="2"/>
     </row>
+    <row r="44" spans="1:18" ht="57.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A44" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="B44" s="4">
+        <v>51</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A45" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="B45" s="4">
+        <v>52</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D28:J28"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="D2:J2"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="C23:C43"/>
-    <mergeCell ref="D16:J16"/>
-    <mergeCell ref="D27:J27"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="D25:J25"/>
     <mergeCell ref="K1:K2"/>
@@ -3056,6 +3098,14 @@
     <mergeCell ref="B15:B17"/>
     <mergeCell ref="D20:J20"/>
     <mergeCell ref="B32:B33"/>
+    <mergeCell ref="D28:J28"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="D2:J2"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="C23:C43"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="D27:J27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
